--- a/artfynd/A 11757-2025 artfynd.xlsx
+++ b/artfynd/A 11757-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129126611</v>
       </c>
       <c r="B2" t="n">
-        <v>92153</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129127178</v>
       </c>
       <c r="B3" t="n">
-        <v>96933</v>
+        <v>96938</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129126618</v>
       </c>
       <c r="B4" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129128166</v>
       </c>
       <c r="B5" t="n">
-        <v>92153</v>
+        <v>92158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129127936</v>
       </c>
       <c r="B6" t="n">
-        <v>96933</v>
+        <v>96938</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 11757-2025 artfynd.xlsx
+++ b/artfynd/A 11757-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129126611</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92161</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129127178</v>
       </c>
       <c r="B3" t="n">
-        <v>96938</v>
+        <v>96941</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129126618</v>
       </c>
       <c r="B4" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129128166</v>
       </c>
       <c r="B5" t="n">
-        <v>92158</v>
+        <v>92161</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129127936</v>
       </c>
       <c r="B6" t="n">
-        <v>96938</v>
+        <v>96941</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 11757-2025 artfynd.xlsx
+++ b/artfynd/A 11757-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129126611</v>
       </c>
       <c r="B2" t="n">
-        <v>92161</v>
+        <v>92168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129127178</v>
       </c>
       <c r="B3" t="n">
-        <v>96941</v>
+        <v>96951</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129126618</v>
       </c>
       <c r="B4" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129128166</v>
       </c>
       <c r="B5" t="n">
-        <v>92161</v>
+        <v>92168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129127936</v>
       </c>
       <c r="B6" t="n">
-        <v>96941</v>
+        <v>96951</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 11757-2025 artfynd.xlsx
+++ b/artfynd/A 11757-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129126611</v>
       </c>
       <c r="B2" t="n">
-        <v>92168</v>
+        <v>92175</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129127178</v>
       </c>
       <c r="B3" t="n">
-        <v>96951</v>
+        <v>96958</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129126618</v>
       </c>
       <c r="B4" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129128166</v>
       </c>
       <c r="B5" t="n">
-        <v>92168</v>
+        <v>92175</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129127936</v>
       </c>
       <c r="B6" t="n">
-        <v>96951</v>
+        <v>96958</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 11757-2025 artfynd.xlsx
+++ b/artfynd/A 11757-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129126611</v>
       </c>
       <c r="B2" t="n">
-        <v>92175</v>
+        <v>92177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129127178</v>
       </c>
       <c r="B3" t="n">
-        <v>96958</v>
+        <v>96960</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129126618</v>
       </c>
       <c r="B4" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129128166</v>
       </c>
       <c r="B5" t="n">
-        <v>92175</v>
+        <v>92177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129127936</v>
       </c>
       <c r="B6" t="n">
-        <v>96958</v>
+        <v>96960</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 11757-2025 artfynd.xlsx
+++ b/artfynd/A 11757-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129126611</v>
       </c>
       <c r="B2" t="n">
-        <v>92177</v>
+        <v>92192</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129127178</v>
       </c>
       <c r="B3" t="n">
-        <v>96960</v>
+        <v>96986</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129126618</v>
       </c>
       <c r="B4" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129128166</v>
       </c>
       <c r="B5" t="n">
-        <v>92177</v>
+        <v>92192</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129127936</v>
       </c>
       <c r="B6" t="n">
-        <v>96960</v>
+        <v>96986</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 11757-2025 artfynd.xlsx
+++ b/artfynd/A 11757-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129126611</v>
       </c>
       <c r="B2" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129127178</v>
       </c>
       <c r="B3" t="n">
-        <v>96986</v>
+        <v>96987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129126618</v>
       </c>
       <c r="B4" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129128166</v>
       </c>
       <c r="B5" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129127936</v>
       </c>
       <c r="B6" t="n">
-        <v>96986</v>
+        <v>96987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 11757-2025 artfynd.xlsx
+++ b/artfynd/A 11757-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129127178</v>
       </c>
       <c r="B3" t="n">
-        <v>96987</v>
+        <v>96988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129127936</v>
       </c>
       <c r="B6" t="n">
-        <v>96987</v>
+        <v>96988</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 11757-2025 artfynd.xlsx
+++ b/artfynd/A 11757-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129126611</v>
       </c>
       <c r="B2" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129127178</v>
       </c>
       <c r="B3" t="n">
-        <v>96988</v>
+        <v>96992</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129126618</v>
       </c>
       <c r="B4" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129128166</v>
       </c>
       <c r="B5" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129127936</v>
       </c>
       <c r="B6" t="n">
-        <v>96988</v>
+        <v>96992</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 11757-2025 artfynd.xlsx
+++ b/artfynd/A 11757-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129126611</v>
       </c>
       <c r="B2" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129127178</v>
       </c>
       <c r="B3" t="n">
-        <v>96992</v>
+        <v>96994</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129126618</v>
       </c>
       <c r="B4" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129128166</v>
       </c>
       <c r="B5" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129127936</v>
       </c>
       <c r="B6" t="n">
-        <v>96992</v>
+        <v>96994</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 11757-2025 artfynd.xlsx
+++ b/artfynd/A 11757-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129126611</v>
       </c>
       <c r="B2" t="n">
-        <v>92198</v>
+        <v>92202</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129127178</v>
       </c>
       <c r="B3" t="n">
-        <v>96994</v>
+        <v>96998</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129126618</v>
       </c>
       <c r="B4" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129128166</v>
       </c>
       <c r="B5" t="n">
-        <v>92198</v>
+        <v>92202</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129127936</v>
       </c>
       <c r="B6" t="n">
-        <v>96994</v>
+        <v>96998</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 11757-2025 artfynd.xlsx
+++ b/artfynd/A 11757-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129126611</v>
       </c>
       <c r="B2" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129127178</v>
       </c>
       <c r="B3" t="n">
-        <v>96998</v>
+        <v>97006</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129126618</v>
       </c>
       <c r="B4" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129128166</v>
       </c>
       <c r="B5" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129127936</v>
       </c>
       <c r="B6" t="n">
-        <v>96998</v>
+        <v>97006</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 11757-2025 artfynd.xlsx
+++ b/artfynd/A 11757-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129126611</v>
       </c>
       <c r="B2" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129127178</v>
       </c>
       <c r="B3" t="n">
-        <v>97006</v>
+        <v>97009</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129126618</v>
       </c>
       <c r="B4" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129128166</v>
       </c>
       <c r="B5" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129127936</v>
       </c>
       <c r="B6" t="n">
-        <v>97006</v>
+        <v>97009</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 11757-2025 artfynd.xlsx
+++ b/artfynd/A 11757-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129126611</v>
       </c>
       <c r="B2" t="n">
-        <v>92206</v>
+        <v>92234</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129127178</v>
       </c>
       <c r="B3" t="n">
-        <v>97009</v>
+        <v>97038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129126618</v>
       </c>
       <c r="B4" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129128166</v>
       </c>
       <c r="B5" t="n">
-        <v>92206</v>
+        <v>92234</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129127936</v>
       </c>
       <c r="B6" t="n">
-        <v>97009</v>
+        <v>97038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 11757-2025 artfynd.xlsx
+++ b/artfynd/A 11757-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129126611</v>
+        <v>129127178</v>
       </c>
       <c r="B2" t="n">
-        <v>92234</v>
+        <v>97394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>2590</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596999</v>
+        <v>597165</v>
       </c>
       <c r="R2" t="n">
-        <v>6504062</v>
+        <v>6504133</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129127178</v>
+        <v>129127936</v>
       </c>
       <c r="B3" t="n">
-        <v>97038</v>
+        <v>97394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,20 +800,29 @@
           <t>(Mart.) Dumort</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597165</v>
+        <v>597177</v>
       </c>
       <c r="R3" t="n">
-        <v>6504133</v>
+        <v>6504017</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,11 +881,11 @@
         <v>129126618</v>
       </c>
       <c r="B4" t="n">
-        <v>92863</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -966,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129128166</v>
+        <v>129126611</v>
       </c>
       <c r="B5" t="n">
-        <v>92234</v>
+        <v>92567</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,13 +1010,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597098</v>
+        <v>596999</v>
       </c>
       <c r="R5" t="n">
-        <v>6503938</v>
+        <v>6504062</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129127936</v>
+        <v>129128166</v>
       </c>
       <c r="B6" t="n">
-        <v>97038</v>
+        <v>92567</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,46 +1083,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2590</v>
+        <v>6031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597177</v>
+        <v>597098</v>
       </c>
       <c r="R6" t="n">
-        <v>6504017</v>
+        <v>6503938</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 11757-2025 artfynd.xlsx
+++ b/artfynd/A 11757-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129127178</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129127936</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129126618</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129126611</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,8 +1191,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129128166</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>